--- a/research/traditional_assets/database/data/canada/canada_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.05499999999999999</v>
+        <v>0.171</v>
       </c>
       <c r="E2">
-        <v>0.253</v>
+        <v>0.09964999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1082373279669372</v>
+        <v>0.179739799643883</v>
       </c>
       <c r="H2">
-        <v>0.1082373279669372</v>
+        <v>0.179739799643883</v>
       </c>
       <c r="I2">
-        <v>0.1258484718287557</v>
+        <v>0.06450913020536568</v>
       </c>
       <c r="J2">
-        <v>0.09728087689624723</v>
+        <v>0.04666447223662583</v>
       </c>
       <c r="K2">
-        <v>1632.43</v>
+        <v>2233.71</v>
       </c>
       <c r="L2">
-        <v>0.1102382463770073</v>
+        <v>0.05145291585181294</v>
       </c>
       <c r="M2">
-        <v>567.33</v>
+        <v>3674.65</v>
       </c>
       <c r="N2">
-        <v>0.02089243890582881</v>
+        <v>0.08135408226068552</v>
       </c>
       <c r="O2">
-        <v>0.347537107257279</v>
+        <v>1.645088216464984</v>
       </c>
       <c r="P2">
-        <v>515.9</v>
+        <v>2176.4</v>
       </c>
       <c r="Q2">
-        <v>0.01899848277284311</v>
+        <v>0.04818391537484005</v>
       </c>
       <c r="R2">
-        <v>0.3160319278621441</v>
+        <v>0.9743431331730619</v>
       </c>
       <c r="S2">
-        <v>51.43000000000001</v>
+        <v>1498.25</v>
       </c>
       <c r="T2">
-        <v>0.09065270653764125</v>
+        <v>0.4077259058685861</v>
       </c>
       <c r="U2">
-        <v>2794.17</v>
+        <v>6504.599999999999</v>
       </c>
       <c r="V2">
-        <v>0.102897830217862</v>
+        <v>0.1440071199904358</v>
       </c>
       <c r="W2">
-        <v>0.2396432020418018</v>
+        <v>0.1785341975252686</v>
       </c>
       <c r="X2">
-        <v>0.04954989929821331</v>
+        <v>0.08164271186569566</v>
       </c>
       <c r="Y2">
-        <v>0.1900933027435884</v>
+        <v>0.0968914856595729</v>
       </c>
       <c r="Z2">
-        <v>2.166394874554303</v>
+        <v>1.608824993414218</v>
       </c>
       <c r="AA2">
-        <v>0.6758589972272976</v>
+        <v>0.1142602983116918</v>
       </c>
       <c r="AB2">
-        <v>0.04762783281932036</v>
+        <v>0.07946079453918992</v>
       </c>
       <c r="AC2">
-        <v>0.6282311644079772</v>
+        <v>0.03646283971610993</v>
       </c>
       <c r="AD2">
-        <v>4850.5</v>
+        <v>12443.18</v>
       </c>
       <c r="AE2">
-        <v>301.8032973270966</v>
+        <v>350.1724156676062</v>
       </c>
       <c r="AF2">
-        <v>5152.303297327097</v>
+        <v>12793.3524156676</v>
       </c>
       <c r="AG2">
-        <v>2358.133297327096</v>
+        <v>6288.752415667605</v>
       </c>
       <c r="AH2">
-        <v>0.1594789619456031</v>
+        <v>0.2207198322775865</v>
       </c>
       <c r="AI2">
-        <v>0.2591727503671951</v>
+        <v>0.2857352231160717</v>
       </c>
       <c r="AJ2">
-        <v>0.07990169169462617</v>
+        <v>0.1222129029272175</v>
       </c>
       <c r="AK2">
-        <v>0.1380184893524553</v>
+        <v>0.1643308335290696</v>
       </c>
       <c r="AL2">
-        <v>111.71</v>
+        <v>572.534</v>
       </c>
       <c r="AM2">
-        <v>111.71</v>
+        <v>572.534</v>
       </c>
       <c r="AN2">
-        <v>2.204412005308222</v>
+        <v>3.745610417601073</v>
       </c>
       <c r="AO2">
-        <v>16.82973771372303</v>
+        <v>4.893770500965881</v>
       </c>
       <c r="AP2">
-        <v>1.071703401864739</v>
+        <v>1.893022246872464</v>
       </c>
       <c r="AQ2">
-        <v>16.82973771372303</v>
+        <v>4.893770500965881</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Definity Financial Corporation (TSX:DFY)</t>
+          <t>Trisura Group Ltd. (TSX:TSU)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,32 +721,35 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.404</v>
+      </c>
       <c r="G3">
-        <v>0.07230892002128037</v>
+        <v>0.1862912400455062</v>
       </c>
       <c r="H3">
-        <v>0.07230892002128037</v>
+        <v>0.1862912400455062</v>
       </c>
       <c r="I3">
-        <v>0.1121652775314772</v>
+        <v>0.2093287827076223</v>
       </c>
       <c r="J3">
-        <v>0.0853874800496542</v>
+        <v>0.1591014881050999</v>
       </c>
       <c r="K3">
-        <v>192.6</v>
+        <v>54.8</v>
       </c>
       <c r="L3">
-        <v>0.0853874800496542</v>
+        <v>0.1558589306029579</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.55</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.001012211846143799</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.02828467153284672</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,55 +761,79 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.55</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>207.8</v>
+        <v>280.1</v>
       </c>
       <c r="V3">
-        <v>0.07684058721295714</v>
+        <v>0.1829164761966956</v>
+      </c>
+      <c r="W3">
+        <v>0.1981200289226319</v>
       </c>
       <c r="X3">
-        <v>0.04799359994984585</v>
+        <v>0.0810453210547248</v>
+      </c>
+      <c r="Y3">
+        <v>0.1170747078679071</v>
+      </c>
+      <c r="Z3">
+        <v>2.345563709139426</v>
+      </c>
+      <c r="AA3">
+        <v>0.3731826765694002</v>
       </c>
       <c r="AB3">
-        <v>0.04783340989370711</v>
+        <v>0.07946079453918992</v>
+      </c>
+      <c r="AC3">
+        <v>0.2937218820302103</v>
       </c>
       <c r="AD3">
-        <v>17.3</v>
+        <v>63.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.3</v>
+        <v>63.5</v>
       </c>
       <c r="AG3">
-        <v>-190.5</v>
+        <v>-216.6</v>
       </c>
       <c r="AH3">
-        <v>0.006356554967666078</v>
+        <v>0.03981690494105844</v>
       </c>
       <c r="AI3">
-        <v>0.01081182426098369</v>
+        <v>0.1421217547000895</v>
       </c>
       <c r="AJ3">
-        <v>-0.07578168509825761</v>
+        <v>-0.1647524149996197</v>
       </c>
       <c r="AK3">
-        <v>-0.1368239603533721</v>
+        <v>-1.299340131973606</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AN3">
-        <v>0.06689868522815158</v>
+        <v>0.8421750663129973</v>
+      </c>
+      <c r="AO3">
+        <v>38.33333333333333</v>
       </c>
       <c r="AP3">
-        <v>-0.7366589327146171</v>
+        <v>-2.872679045092838</v>
+      </c>
+      <c r="AQ3">
+        <v>38.33333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -826,112 +853,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.24</v>
+        <v>-0.2</v>
       </c>
       <c r="G4">
-        <v>0.1158690176322418</v>
+        <v>0.1456439393939394</v>
       </c>
       <c r="H4">
-        <v>0.1158690176322418</v>
+        <v>0.1456439393939394</v>
       </c>
       <c r="I4">
-        <v>0.1272040302267002</v>
+        <v>0.112689393939394</v>
       </c>
       <c r="J4">
-        <v>0.09395465994962215</v>
+        <v>0.08123670350767953</v>
       </c>
       <c r="K4">
-        <v>3.33</v>
+        <v>4.21</v>
       </c>
       <c r="L4">
-        <v>0.08387909319899244</v>
+        <v>0.07973484848484849</v>
       </c>
       <c r="M4">
-        <v>53.2</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>2.283261802575107</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>15.97597597597598</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>53.2</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>2.283261802575107</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>15.97597597597598</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>8.57</v>
+        <v>20.8</v>
       </c>
       <c r="V4">
-        <v>0.3678111587982832</v>
+        <v>0.4727272727272727</v>
       </c>
       <c r="W4">
-        <v>0.2378571428571429</v>
+        <v>0.2115577889447236</v>
       </c>
       <c r="X4">
-        <v>0.05021504124041424</v>
+        <v>0.08164271186569566</v>
       </c>
       <c r="Y4">
-        <v>0.1876421016167286</v>
+        <v>0.129915077079028</v>
       </c>
       <c r="Z4">
-        <v>10.70658036677454</v>
+        <v>3.960693121296227</v>
       </c>
       <c r="AA4">
-        <v>1.005933117583603</v>
+        <v>0.3217536527796474</v>
       </c>
       <c r="AB4">
-        <v>0.04755013649925784</v>
+        <v>0.07948730338668827</v>
       </c>
       <c r="AC4">
-        <v>0.9583829810843452</v>
+        <v>0.2422663493929591</v>
       </c>
       <c r="AD4">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.3</v>
+        <v>2.68</v>
       </c>
       <c r="AG4">
-        <v>-6.27</v>
+        <v>-18.12</v>
       </c>
       <c r="AH4">
-        <v>0.08984374999999999</v>
+        <v>0.05741216795201371</v>
       </c>
       <c r="AI4">
-        <v>0.1036036036036036</v>
+        <v>0.1117597998331943</v>
       </c>
       <c r="AJ4">
-        <v>-0.3681738109219025</v>
+        <v>-0.7001545595054096</v>
       </c>
       <c r="AK4">
-        <v>-0.4600146735143067</v>
+        <v>-5.698113207547171</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="AN4">
-        <v>0.4291044776119403</v>
+        <v>0.4207221350078493</v>
+      </c>
+      <c r="AO4">
+        <v>52.19298245614035</v>
       </c>
       <c r="AP4">
-        <v>-1.169776119402985</v>
+        <v>-2.84458398744113</v>
+      </c>
+      <c r="AQ4">
+        <v>52.19298245614035</v>
       </c>
     </row>
     <row r="5">
@@ -942,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Trisura Group Ltd. (TSX:TSU)</t>
+          <t>Intact Financial Corporation (TSX:IFC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -950,116 +980,122 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.194</v>
+      </c>
+      <c r="E5">
+        <v>0.299</v>
+      </c>
       <c r="G5">
-        <v>0.1137846655791191</v>
+        <v>0.1649397020419008</v>
       </c>
       <c r="H5">
-        <v>0.1137846655791191</v>
+        <v>0.1649397020419008</v>
       </c>
       <c r="I5">
-        <v>0.2573409461663948</v>
+        <v>0.1125777145010905</v>
       </c>
       <c r="J5">
-        <v>0.2001096004404314</v>
+        <v>0.09112993045267812</v>
       </c>
       <c r="K5">
-        <v>50</v>
+        <v>1969.5</v>
       </c>
       <c r="L5">
-        <v>0.2039151712887439</v>
+        <v>0.1276268978790412</v>
       </c>
       <c r="M5">
-        <v>1.63</v>
+        <v>678.0999999999999</v>
       </c>
       <c r="N5">
-        <v>0.001051884357253485</v>
+        <v>0.02686683069657241</v>
       </c>
       <c r="O5">
-        <v>0.0326</v>
+        <v>0.3443005839045443</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>500.4</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.01982622338971366</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.254074638233054</v>
       </c>
       <c r="S5">
-        <v>1.63</v>
+        <v>177.6999999999999</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0.2620557439905618</v>
       </c>
       <c r="U5">
-        <v>194</v>
+        <v>954.1</v>
       </c>
       <c r="V5">
-        <v>0.1251935983479608</v>
+        <v>0.03780215774605476</v>
       </c>
       <c r="W5">
-        <v>0.2414292612264607</v>
+        <v>0.1785341975252686</v>
       </c>
       <c r="X5">
-        <v>0.04888475735601238</v>
+        <v>0.08500182019330021</v>
       </c>
       <c r="Y5">
-        <v>0.1925445038704483</v>
+        <v>0.09353237733196834</v>
       </c>
       <c r="Z5">
-        <v>1.727977448907682</v>
+        <v>1.253817464186751</v>
       </c>
       <c r="AA5">
-        <v>0.3457848768709921</v>
+        <v>0.1142602983116918</v>
       </c>
       <c r="AB5">
-        <v>0.04770552913938287</v>
+        <v>0.07779745859558189</v>
       </c>
       <c r="AC5">
-        <v>0.2980793477316093</v>
+        <v>0.03646283971610993</v>
       </c>
       <c r="AD5">
-        <v>67.3</v>
+        <v>3946.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>350.1724156676062</v>
       </c>
       <c r="AF5">
-        <v>67.3</v>
+        <v>4296.372415667606</v>
       </c>
       <c r="AG5">
-        <v>-126.7</v>
+        <v>3342.272415667606</v>
       </c>
       <c r="AH5">
-        <v>0.041622858556497</v>
+        <v>0.1454638430167764</v>
       </c>
       <c r="AI5">
-        <v>0.1956964233788892</v>
+        <v>0.2764972418788972</v>
       </c>
       <c r="AJ5">
-        <v>-0.08904350270574181</v>
+        <v>0.116938017512132</v>
       </c>
       <c r="AK5">
-        <v>-0.8452301534356236</v>
+        <v>0.2291664943654126</v>
       </c>
       <c r="AL5">
-        <v>1.01</v>
+        <v>123.1</v>
       </c>
       <c r="AM5">
-        <v>1.01</v>
+        <v>123.1</v>
       </c>
       <c r="AN5">
-        <v>1.05320813771518</v>
+        <v>1.862293534686173</v>
       </c>
       <c r="AO5">
-        <v>62.47524752475248</v>
+        <v>14.12347684809098</v>
       </c>
       <c r="AP5">
-        <v>-1.982785602503913</v>
+        <v>1.577287595879002</v>
       </c>
       <c r="AQ5">
-        <v>62.47524752475248</v>
+        <v>14.12347684809098</v>
       </c>
     </row>
     <row r="6">
@@ -1070,7 +1106,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intact Financial Corporation (TSX:IFC)</t>
+          <t>Definity Financial Corporation (TSX:DFY)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1078,122 +1114,244 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.13</v>
-      </c>
-      <c r="E6">
-        <v>0.253</v>
-      </c>
       <c r="G6">
-        <v>0.1147077284250511</v>
+        <v>0.09705038743096878</v>
       </c>
       <c r="H6">
-        <v>0.1147077284250511</v>
+        <v>0.09705038743096878</v>
       </c>
       <c r="I6">
-        <v>0.125731746010628</v>
+        <v>0.05732265936041783</v>
       </c>
       <c r="J6">
-        <v>0.1024105942183538</v>
+        <v>0.04490774433837065</v>
       </c>
       <c r="K6">
-        <v>1386.5</v>
+        <v>104.9</v>
       </c>
       <c r="L6">
-        <v>0.1130203705666099</v>
+        <v>0.04490774433837065</v>
       </c>
       <c r="M6">
-        <v>512.5</v>
+        <v>1455.5</v>
       </c>
       <c r="N6">
-        <v>0.02240182536629717</v>
+        <v>0.442845407247391</v>
       </c>
       <c r="O6">
-        <v>0.3696357735304724</v>
+        <v>13.87511916110581</v>
       </c>
       <c r="P6">
-        <v>462.7</v>
+        <v>1426.1</v>
       </c>
       <c r="Q6">
-        <v>0.02022502360387453</v>
+        <v>0.4339002647031978</v>
       </c>
       <c r="R6">
-        <v>0.3337179949513163</v>
+        <v>13.59485224022879</v>
       </c>
       <c r="S6">
-        <v>49.80000000000001</v>
+        <v>29.40000000000009</v>
       </c>
       <c r="T6">
-        <v>0.09717073170731709</v>
+        <v>0.02019924424596365</v>
       </c>
       <c r="U6">
-        <v>2383.8</v>
+        <v>141.2</v>
       </c>
       <c r="V6">
-        <v>0.1041979927964472</v>
+        <v>0.04296102473605744</v>
       </c>
       <c r="W6">
-        <v>0.2297622006794266</v>
+        <v>0.06534197084838669</v>
       </c>
       <c r="X6">
-        <v>0.05316766990661544</v>
+        <v>0.0799159924895551</v>
       </c>
       <c r="Y6">
-        <v>0.1765945307728112</v>
+        <v>-0.0145740216411684</v>
       </c>
       <c r="Z6">
-        <v>1.833790838798137</v>
+        <v>1.726970279461777</v>
       </c>
       <c r="AA6">
-        <v>0.1877996094734908</v>
+        <v>0.07755433979003401</v>
       </c>
       <c r="AB6">
-        <v>0.04664022389493681</v>
+        <v>0.07970739356048112</v>
       </c>
       <c r="AC6">
-        <v>0.141159385578554</v>
+        <v>-0.002153053770447111</v>
       </c>
       <c r="AD6">
-        <v>4763.6</v>
+        <v>15.5</v>
       </c>
       <c r="AE6">
-        <v>301.8032973270966</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>5065.403297327097</v>
+        <v>15.5</v>
       </c>
       <c r="AG6">
-        <v>2681.603297327097</v>
+        <v>-125.7</v>
       </c>
       <c r="AH6">
-        <v>0.1812762659556939</v>
+        <v>0.004693840469989704</v>
       </c>
       <c r="AI6">
-        <v>0.2827685314479923</v>
+        <v>0.009407052254658007</v>
       </c>
       <c r="AJ6">
-        <v>0.1049173272786453</v>
+        <v>-0.03976589686807972</v>
       </c>
       <c r="AK6">
-        <v>0.1726746466768603</v>
+        <v>-0.0834384334550282</v>
       </c>
       <c r="AL6">
-        <v>110.7</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>110.7</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>2.543978638184246</v>
-      </c>
-      <c r="AO6">
-        <v>14.08220415537489</v>
+        <v>0.1129737609329446</v>
       </c>
       <c r="AP6">
-        <v>1.432097889093243</v>
-      </c>
-      <c r="AQ6">
-        <v>14.08220415537489</v>
+        <v>-0.9161807580174927</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fairfax Financial Holdings Limited (TSX:FFH)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.148</v>
+      </c>
+      <c r="E7">
+        <v>-0.09970000000000001</v>
+      </c>
+      <c r="G7">
+        <v>0.1964208599603022</v>
+      </c>
+      <c r="H7">
+        <v>0.1964208599603022</v>
+      </c>
+      <c r="I7">
+        <v>0.03366784597891501</v>
+      </c>
+      <c r="J7">
+        <v>0.01828291889234752</v>
+      </c>
+      <c r="K7">
+        <v>100.3</v>
+      </c>
+      <c r="L7">
+        <v>0.003973740823352759</v>
+      </c>
+      <c r="M7">
+        <v>1539.5</v>
+      </c>
+      <c r="N7">
+        <v>0.1021749085768519</v>
+      </c>
+      <c r="O7">
+        <v>15.34895314057827</v>
+      </c>
+      <c r="P7">
+        <v>249.9</v>
+      </c>
+      <c r="Q7">
+        <v>0.01658558600412815</v>
+      </c>
+      <c r="R7">
+        <v>2.491525423728814</v>
+      </c>
+      <c r="S7">
+        <v>1289.6</v>
+      </c>
+      <c r="T7">
+        <v>0.8376745696654757</v>
+      </c>
+      <c r="U7">
+        <v>5108.4</v>
+      </c>
+      <c r="V7">
+        <v>0.3390388457122377</v>
+      </c>
+      <c r="W7">
+        <v>0.0068984490525809</v>
+      </c>
+      <c r="X7">
+        <v>0.09693327330715126</v>
+      </c>
+      <c r="Y7">
+        <v>-0.09003482425457036</v>
+      </c>
+      <c r="Z7">
+        <v>1.917913453136279</v>
+      </c>
+      <c r="AA7">
+        <v>0.03506505610623274</v>
+      </c>
+      <c r="AB7">
+        <v>0.07799977169908104</v>
+      </c>
+      <c r="AC7">
+        <v>-0.0429347155928483</v>
+      </c>
+      <c r="AD7">
+        <v>8415.299999999999</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>8415.299999999999</v>
+      </c>
+      <c r="AG7">
+        <v>3306.9</v>
+      </c>
+      <c r="AH7">
+        <v>0.358363213613484</v>
+      </c>
+      <c r="AI7">
+        <v>0.3103398681240873</v>
+      </c>
+      <c r="AJ7">
+        <v>0.1799751825929836</v>
+      </c>
+      <c r="AK7">
+        <v>0.1502589967284624</v>
+      </c>
+      <c r="AL7">
+        <v>447.4</v>
+      </c>
+      <c r="AM7">
+        <v>447.4</v>
+      </c>
+      <c r="AN7">
+        <v>8.551265115333807</v>
+      </c>
+      <c r="AO7">
+        <v>1.899418864550737</v>
+      </c>
+      <c r="AP7">
+        <v>3.360329234833858</v>
+      </c>
+      <c r="AQ7">
+        <v>1.899418864550737</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.171</v>
+        <v>0.139</v>
       </c>
       <c r="E2">
-        <v>0.09964999999999999</v>
+        <v>0.112</v>
+      </c>
+      <c r="F2">
+        <v>0.103</v>
       </c>
       <c r="G2">
-        <v>0.179739799643883</v>
+        <v>0.08526455216601124</v>
       </c>
       <c r="H2">
-        <v>0.179739799643883</v>
+        <v>0.08526455216601124</v>
       </c>
       <c r="I2">
-        <v>0.06450913020536568</v>
+        <v>0.1029742072998713</v>
       </c>
       <c r="J2">
-        <v>0.04666447223662583</v>
+        <v>0.07651673278016398</v>
       </c>
       <c r="K2">
-        <v>2233.71</v>
+        <v>4305.1</v>
       </c>
       <c r="L2">
-        <v>0.05145291585181294</v>
+        <v>0.0884085798482406</v>
       </c>
       <c r="M2">
-        <v>3674.65</v>
+        <v>1277.5</v>
       </c>
       <c r="N2">
-        <v>0.08135408226068552</v>
+        <v>0.02373988151429782</v>
       </c>
       <c r="O2">
-        <v>1.645088216464984</v>
+        <v>0.2967410745394997</v>
       </c>
       <c r="P2">
-        <v>2176.4</v>
+        <v>850.5</v>
       </c>
       <c r="Q2">
-        <v>0.04818391537484005</v>
+        <v>0.01580490741910786</v>
       </c>
       <c r="R2">
-        <v>0.9743431331730619</v>
+        <v>0.1975563866112285</v>
       </c>
       <c r="S2">
-        <v>1498.25</v>
+        <v>427.0000000000001</v>
       </c>
       <c r="T2">
-        <v>0.4077259058685861</v>
+        <v>0.3342465753424658</v>
       </c>
       <c r="U2">
-        <v>6504.599999999999</v>
+        <v>6216.8</v>
       </c>
       <c r="V2">
-        <v>0.1440071199904358</v>
+        <v>0.1155272762411638</v>
       </c>
       <c r="W2">
-        <v>0.1785341975252686</v>
+        <v>0.1426423672643327</v>
       </c>
       <c r="X2">
-        <v>0.08164271186569566</v>
+        <v>0.07153970318863109</v>
       </c>
       <c r="Y2">
-        <v>0.0968914856595729</v>
+        <v>0.07110266407570157</v>
       </c>
       <c r="Z2">
-        <v>1.608824993414218</v>
+        <v>1.543429326846343</v>
       </c>
       <c r="AA2">
-        <v>0.1142602983116918</v>
+        <v>0.1530012084833439</v>
       </c>
       <c r="AB2">
-        <v>0.07946079453918992</v>
+        <v>0.06799391359697232</v>
       </c>
       <c r="AC2">
-        <v>0.03646283971610993</v>
+        <v>0.08512285167477601</v>
       </c>
       <c r="AD2">
-        <v>12443.18</v>
+        <v>12927.4</v>
       </c>
       <c r="AE2">
-        <v>350.1724156676062</v>
+        <v>292.5974421455962</v>
       </c>
       <c r="AF2">
-        <v>12793.3524156676</v>
+        <v>13219.9974421456</v>
       </c>
       <c r="AG2">
-        <v>6288.752415667605</v>
+        <v>7003.197442145595</v>
       </c>
       <c r="AH2">
-        <v>0.2207198322775865</v>
+        <v>0.1972180310805015</v>
       </c>
       <c r="AI2">
-        <v>0.2857352231160717</v>
+        <v>0.2498520747218614</v>
       </c>
       <c r="AJ2">
-        <v>0.1222129029272175</v>
+        <v>0.1151546270479016</v>
       </c>
       <c r="AK2">
-        <v>0.1643308335290696</v>
+        <v>0.1499790730336598</v>
       </c>
       <c r="AL2">
-        <v>572.534</v>
+        <v>695.5599999999999</v>
       </c>
       <c r="AM2">
-        <v>572.534</v>
+        <v>695.5599999999999</v>
       </c>
       <c r="AN2">
-        <v>3.745610417601073</v>
+        <v>2.210340936292446</v>
       </c>
       <c r="AO2">
-        <v>4.893770500965881</v>
+        <v>7.194490770027029</v>
       </c>
       <c r="AP2">
-        <v>1.893022246872464</v>
+        <v>1.197414328582156</v>
       </c>
       <c r="AQ2">
-        <v>4.893770500965881</v>
+        <v>7.194490770027029</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Trisura Group Ltd. (TSX:TSU)</t>
+          <t>Definity Financial Corporation (TSX:DFY)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,119 +724,116 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.404</v>
-      </c>
       <c r="G3">
-        <v>0.1862912400455062</v>
+        <v>0.0771151834227667</v>
       </c>
       <c r="H3">
-        <v>0.1862912400455062</v>
+        <v>0.0771151834227667</v>
       </c>
       <c r="I3">
-        <v>0.2093287827076223</v>
+        <v>0.1442408288616651</v>
       </c>
       <c r="J3">
-        <v>0.1591014881050999</v>
+        <v>0.1130918065841694</v>
       </c>
       <c r="K3">
-        <v>54.8</v>
+        <v>332.9</v>
       </c>
       <c r="L3">
-        <v>0.1558589306029579</v>
+        <v>0.1123485538793831</v>
       </c>
       <c r="M3">
-        <v>1.55</v>
+        <v>59.1</v>
       </c>
       <c r="N3">
-        <v>0.001012211846143799</v>
+        <v>0.01806455556914048</v>
       </c>
       <c r="O3">
-        <v>0.02828467153284672</v>
+        <v>0.1775307900270352</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>45.7</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01396870033011371</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.1372784620006008</v>
       </c>
       <c r="S3">
-        <v>1.55</v>
+        <v>13.4</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.2267343485617597</v>
       </c>
       <c r="U3">
-        <v>280.1</v>
+        <v>299.5</v>
       </c>
       <c r="V3">
-        <v>0.1829164761966956</v>
+        <v>0.09154542120063577</v>
       </c>
       <c r="W3">
-        <v>0.1981200289226319</v>
+        <v>0.203957848302904</v>
       </c>
       <c r="X3">
-        <v>0.0810453210547248</v>
+        <v>0.06993001987997857</v>
       </c>
       <c r="Y3">
-        <v>0.1170747078679071</v>
+        <v>0.1340278284229255</v>
       </c>
       <c r="Z3">
-        <v>2.345563709139426</v>
+        <v>1.966876866910056</v>
       </c>
       <c r="AA3">
-        <v>0.3731826765694002</v>
+        <v>0.2224376582074691</v>
       </c>
       <c r="AB3">
-        <v>0.07946079453918992</v>
+        <v>0.06872587178532845</v>
       </c>
       <c r="AC3">
-        <v>0.2937218820302103</v>
+        <v>0.1537117864221407</v>
       </c>
       <c r="AD3">
-        <v>63.5</v>
+        <v>110.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>63.5</v>
+        <v>110.6</v>
       </c>
       <c r="AG3">
-        <v>-216.6</v>
+        <v>-188.9</v>
       </c>
       <c r="AH3">
-        <v>0.03981690494105844</v>
+        <v>0.03270060907101886</v>
       </c>
       <c r="AI3">
-        <v>0.1421217547000895</v>
+        <v>0.05090206185567011</v>
       </c>
       <c r="AJ3">
-        <v>-0.1647524149996197</v>
+        <v>-0.06127745158464983</v>
       </c>
       <c r="AK3">
-        <v>-1.299340131973606</v>
+        <v>-0.1008380932045054</v>
       </c>
       <c r="AL3">
-        <v>1.92</v>
+        <v>2.66</v>
       </c>
       <c r="AM3">
-        <v>1.92</v>
+        <v>2.66</v>
       </c>
       <c r="AN3">
-        <v>0.8421750663129973</v>
+        <v>0.2435050638485249</v>
       </c>
       <c r="AO3">
-        <v>38.33333333333333</v>
+        <v>160.6766917293233</v>
       </c>
       <c r="AP3">
-        <v>-2.872679045092838</v>
+        <v>-0.4158960810215764</v>
       </c>
       <c r="AQ3">
-        <v>38.33333333333333</v>
+        <v>160.6766917293233</v>
       </c>
     </row>
     <row r="4">
@@ -844,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ICPEI Holdings Inc. (TSXV:ICPH)</t>
+          <t>Trisura Group Ltd. (TSX:TSU)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -853,34 +853,37 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.2</v>
+        <v>0.6409999999999999</v>
+      </c>
+      <c r="E4">
+        <v>0.112</v>
       </c>
       <c r="G4">
-        <v>0.1456439393939394</v>
+        <v>0.0324630314232902</v>
       </c>
       <c r="H4">
-        <v>0.1456439393939394</v>
+        <v>0.0324630314232902</v>
       </c>
       <c r="I4">
-        <v>0.112689393939394</v>
+        <v>0.05371996303142329</v>
       </c>
       <c r="J4">
-        <v>0.08123670350767953</v>
+        <v>0.03029112754158965</v>
       </c>
       <c r="K4">
-        <v>4.21</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L4">
-        <v>0.07973484848484849</v>
+        <v>0.01005083179297597</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.2</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.0009828814808747644</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.1379310344827586</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -892,76 +895,79 @@
         <v>-0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.2</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>20.8</v>
+        <v>392.9</v>
       </c>
       <c r="V4">
-        <v>0.4727272727272727</v>
+        <v>0.3218117781964124</v>
       </c>
       <c r="W4">
-        <v>0.2115577889447236</v>
+        <v>0.02269762588051135</v>
       </c>
       <c r="X4">
-        <v>0.08164271186569566</v>
+        <v>0.07032365486842609</v>
       </c>
       <c r="Y4">
-        <v>0.129915077079028</v>
+        <v>-0.04762602898791475</v>
       </c>
       <c r="Z4">
-        <v>3.960693121296227</v>
+        <v>5.19256148770246</v>
       </c>
       <c r="AA4">
-        <v>0.3217536527796474</v>
+        <v>0.1572885422915417</v>
       </c>
       <c r="AB4">
-        <v>0.07948730338668827</v>
+        <v>0.06871193839593473</v>
       </c>
       <c r="AC4">
-        <v>0.2422663493929591</v>
+        <v>0.08857660389560698</v>
       </c>
       <c r="AD4">
-        <v>2.68</v>
+        <v>62.8</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.68</v>
+        <v>62.8</v>
       </c>
       <c r="AG4">
-        <v>-18.12</v>
+        <v>-330.1</v>
       </c>
       <c r="AH4">
-        <v>0.05741216795201371</v>
+        <v>0.04892108748149879</v>
       </c>
       <c r="AI4">
-        <v>0.1117597998331943</v>
+        <v>0.1242580134546893</v>
       </c>
       <c r="AJ4">
-        <v>-0.7001545595054096</v>
+        <v>-0.3705657835653344</v>
       </c>
       <c r="AK4">
-        <v>-5.698113207547171</v>
+        <v>-2.93422222222222</v>
       </c>
       <c r="AL4">
-        <v>0.114</v>
+        <v>30.2</v>
       </c>
       <c r="AM4">
-        <v>0.114</v>
+        <v>30.2</v>
       </c>
       <c r="AN4">
-        <v>0.4207221350078493</v>
+        <v>1.365217391304348</v>
       </c>
       <c r="AO4">
-        <v>52.19298245614035</v>
+        <v>1.539735099337748</v>
       </c>
       <c r="AP4">
-        <v>-2.84458398744113</v>
+        <v>-7.176086956521738</v>
       </c>
       <c r="AQ4">
-        <v>52.19298245614035</v>
+        <v>1.539735099337748</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intact Financial Corporation (TSX:IFC)</t>
+          <t>Fairfax Financial Holdings Limited (TSX:FFH)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,121 +987,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.194</v>
+        <v>0.11</v>
       </c>
       <c r="E5">
-        <v>0.299</v>
+        <v>0.128</v>
       </c>
       <c r="G5">
-        <v>0.1649397020419008</v>
+        <v>0.04442959801633994</v>
       </c>
       <c r="H5">
-        <v>0.1649397020419008</v>
+        <v>0.04442959801633994</v>
       </c>
       <c r="I5">
-        <v>0.1125777145010905</v>
+        <v>0.1064987469171503</v>
       </c>
       <c r="J5">
-        <v>0.09112993045267812</v>
+        <v>0.08900203462225631</v>
       </c>
       <c r="K5">
-        <v>1969.5</v>
+        <v>3144.4</v>
       </c>
       <c r="L5">
-        <v>0.1276268978790412</v>
+        <v>0.1045144220861669</v>
       </c>
       <c r="M5">
-        <v>678.0999999999999</v>
+        <v>563</v>
       </c>
       <c r="N5">
-        <v>0.02686683069657241</v>
+        <v>0.02583398338916166</v>
       </c>
       <c r="O5">
-        <v>0.3443005839045443</v>
+        <v>0.179048467116143</v>
       </c>
       <c r="P5">
-        <v>500.4</v>
+        <v>245.2</v>
       </c>
       <c r="Q5">
-        <v>0.01982622338971366</v>
+        <v>0.01125131923094572</v>
       </c>
       <c r="R5">
-        <v>0.254074638233054</v>
+        <v>0.0779799007759827</v>
       </c>
       <c r="S5">
-        <v>177.6999999999999</v>
+        <v>317.8</v>
       </c>
       <c r="T5">
-        <v>0.2620557439905618</v>
+        <v>0.5644760213143872</v>
       </c>
       <c r="U5">
-        <v>954.1</v>
+        <v>4392.6</v>
       </c>
       <c r="V5">
-        <v>0.03780215774605476</v>
+        <v>0.2015601339879778</v>
       </c>
       <c r="W5">
-        <v>0.1785341975252686</v>
+        <v>0.2353011606414583</v>
       </c>
       <c r="X5">
-        <v>0.08500182019330021</v>
+        <v>0.07801831769949268</v>
       </c>
       <c r="Y5">
-        <v>0.09353237733196834</v>
+        <v>0.1572828429419657</v>
       </c>
       <c r="Z5">
-        <v>1.253817464186751</v>
+        <v>1.670904213665673</v>
       </c>
       <c r="AA5">
-        <v>0.1142602983116918</v>
+        <v>0.1487138746751462</v>
       </c>
       <c r="AB5">
-        <v>0.07779745859558189</v>
+        <v>0.06704477522120111</v>
       </c>
       <c r="AC5">
-        <v>0.03646283971610993</v>
+        <v>0.08166909945394504</v>
       </c>
       <c r="AD5">
-        <v>3946.2</v>
+        <v>8632</v>
       </c>
       <c r="AE5">
-        <v>350.1724156676062</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>4296.372415667606</v>
+        <v>8632</v>
       </c>
       <c r="AG5">
-        <v>3342.272415667606</v>
+        <v>4239.4</v>
       </c>
       <c r="AH5">
-        <v>0.1454638430167764</v>
+        <v>0.2837140509449466</v>
       </c>
       <c r="AI5">
-        <v>0.2764972418788972</v>
+        <v>0.2521801370163163</v>
       </c>
       <c r="AJ5">
-        <v>0.116938017512132</v>
+        <v>0.1628509088674114</v>
       </c>
       <c r="AK5">
-        <v>0.2291664943654126</v>
+        <v>0.1420858065013456</v>
       </c>
       <c r="AL5">
-        <v>123.1</v>
+        <v>505.2</v>
       </c>
       <c r="AM5">
-        <v>123.1</v>
+        <v>505.2</v>
       </c>
       <c r="AN5">
-        <v>1.862293534686173</v>
+        <v>2.377175589336858</v>
       </c>
       <c r="AO5">
-        <v>14.12347684809098</v>
+        <v>6.342240696753761</v>
       </c>
       <c r="AP5">
-        <v>1.577287595879002</v>
+        <v>1.167492839832562</v>
       </c>
       <c r="AQ5">
-        <v>14.12347684809098</v>
+        <v>6.342240696753761</v>
       </c>
     </row>
     <row r="6">
@@ -1106,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Definity Financial Corporation (TSX:DFY)</t>
+          <t>Intact Financial Corporation (TSX:IFC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1114,244 +1120,125 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D6">
+        <v>0.139</v>
+      </c>
+      <c r="E6">
+        <v>0.0978</v>
+      </c>
+      <c r="F6">
+        <v>0.103</v>
+      </c>
       <c r="G6">
-        <v>0.09705038743096878</v>
+        <v>0.1731073675664705</v>
       </c>
       <c r="H6">
-        <v>0.09705038743096878</v>
+        <v>0.1731073675664705</v>
       </c>
       <c r="I6">
-        <v>0.05732265936041783</v>
+        <v>0.09041205003523989</v>
       </c>
       <c r="J6">
-        <v>0.04490774433837065</v>
+        <v>0.07130244508336292</v>
       </c>
       <c r="K6">
-        <v>104.9</v>
+        <v>819.1</v>
       </c>
       <c r="L6">
-        <v>0.04490774433837065</v>
+        <v>0.05541573641837494</v>
       </c>
       <c r="M6">
-        <v>1455.5</v>
+        <v>654.2</v>
       </c>
       <c r="N6">
-        <v>0.442845407247391</v>
+        <v>0.02376584359299449</v>
       </c>
       <c r="O6">
-        <v>13.87511916110581</v>
+        <v>0.7986814796728117</v>
       </c>
       <c r="P6">
-        <v>1426.1</v>
+        <v>559.6</v>
       </c>
       <c r="Q6">
-        <v>0.4339002647031978</v>
+        <v>0.02032920525013714</v>
       </c>
       <c r="R6">
-        <v>13.59485224022879</v>
+        <v>0.6831888658283481</v>
       </c>
       <c r="S6">
-        <v>29.40000000000009</v>
+        <v>94.60000000000002</v>
       </c>
       <c r="T6">
-        <v>0.02019924424596365</v>
+        <v>0.1446040966065424</v>
       </c>
       <c r="U6">
-        <v>141.2</v>
+        <v>1131.8</v>
       </c>
       <c r="V6">
-        <v>0.04296102473605744</v>
+        <v>0.04111614457131024</v>
       </c>
       <c r="W6">
-        <v>0.06534197084838669</v>
+        <v>0.08132688622576129</v>
       </c>
       <c r="X6">
-        <v>0.0799159924895551</v>
+        <v>0.07275575150883611</v>
       </c>
       <c r="Y6">
-        <v>-0.0145740216411684</v>
+        <v>0.00857113471692518</v>
       </c>
       <c r="Z6">
-        <v>1.726970279461777</v>
+        <v>1.245104005862439</v>
       </c>
       <c r="AA6">
-        <v>0.07755433979003401</v>
+        <v>0.08877896000108171</v>
       </c>
       <c r="AB6">
-        <v>0.07970739356048112</v>
+        <v>0.06727588879800991</v>
       </c>
       <c r="AC6">
-        <v>-0.002153053770447111</v>
+        <v>0.02150307120307179</v>
       </c>
       <c r="AD6">
-        <v>15.5</v>
+        <v>4122</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>292.5974421455962</v>
       </c>
       <c r="AF6">
-        <v>15.5</v>
+        <v>4414.597442145596</v>
       </c>
       <c r="AG6">
-        <v>-125.7</v>
+        <v>3282.797442145596</v>
       </c>
       <c r="AH6">
-        <v>0.004693840469989704</v>
+        <v>0.1382088441577163</v>
       </c>
       <c r="AI6">
-        <v>0.009407052254658007</v>
+        <v>0.275850317911629</v>
       </c>
       <c r="AJ6">
-        <v>-0.03976589686807972</v>
+        <v>0.106550784807609</v>
       </c>
       <c r="AK6">
-        <v>-0.0834384334550282</v>
+        <v>0.2207397898550169</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>157.5</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>157.5</v>
       </c>
       <c r="AN6">
-        <v>0.1129737609329446</v>
+        <v>2.40041928721174</v>
+      </c>
+      <c r="AO6">
+        <v>8.420317460317461</v>
       </c>
       <c r="AP6">
-        <v>-0.9161807580174927</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Fairfax Financial Holdings Limited (TSX:FFH)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.148</v>
-      </c>
-      <c r="E7">
-        <v>-0.09970000000000001</v>
-      </c>
-      <c r="G7">
-        <v>0.1964208599603022</v>
-      </c>
-      <c r="H7">
-        <v>0.1964208599603022</v>
-      </c>
-      <c r="I7">
-        <v>0.03366784597891501</v>
-      </c>
-      <c r="J7">
-        <v>0.01828291889234752</v>
-      </c>
-      <c r="K7">
-        <v>100.3</v>
-      </c>
-      <c r="L7">
-        <v>0.003973740823352759</v>
-      </c>
-      <c r="M7">
-        <v>1539.5</v>
-      </c>
-      <c r="N7">
-        <v>0.1021749085768519</v>
-      </c>
-      <c r="O7">
-        <v>15.34895314057827</v>
-      </c>
-      <c r="P7">
-        <v>249.9</v>
-      </c>
-      <c r="Q7">
-        <v>0.01658558600412815</v>
-      </c>
-      <c r="R7">
-        <v>2.491525423728814</v>
-      </c>
-      <c r="S7">
-        <v>1289.6</v>
-      </c>
-      <c r="T7">
-        <v>0.8376745696654757</v>
-      </c>
-      <c r="U7">
-        <v>5108.4</v>
-      </c>
-      <c r="V7">
-        <v>0.3390388457122377</v>
-      </c>
-      <c r="W7">
-        <v>0.0068984490525809</v>
-      </c>
-      <c r="X7">
-        <v>0.09693327330715126</v>
-      </c>
-      <c r="Y7">
-        <v>-0.09003482425457036</v>
-      </c>
-      <c r="Z7">
-        <v>1.917913453136279</v>
-      </c>
-      <c r="AA7">
-        <v>0.03506505610623274</v>
-      </c>
-      <c r="AB7">
-        <v>0.07799977169908104</v>
-      </c>
-      <c r="AC7">
-        <v>-0.0429347155928483</v>
-      </c>
-      <c r="AD7">
-        <v>8415.299999999999</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>8415.299999999999</v>
-      </c>
-      <c r="AG7">
-        <v>3306.9</v>
-      </c>
-      <c r="AH7">
-        <v>0.358363213613484</v>
-      </c>
-      <c r="AI7">
-        <v>0.3103398681240873</v>
-      </c>
-      <c r="AJ7">
-        <v>0.1799751825929836</v>
-      </c>
-      <c r="AK7">
-        <v>0.1502589967284624</v>
-      </c>
-      <c r="AL7">
-        <v>447.4</v>
-      </c>
-      <c r="AM7">
-        <v>447.4</v>
-      </c>
-      <c r="AN7">
-        <v>8.551265115333807</v>
-      </c>
-      <c r="AO7">
-        <v>1.899418864550737</v>
-      </c>
-      <c r="AP7">
-        <v>3.360329234833858</v>
-      </c>
-      <c r="AQ7">
-        <v>1.899418864550737</v>
+        <v>1.911715258645234</v>
+      </c>
+      <c r="AQ6">
+        <v>8.420317460317461</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.139</v>
+        <v>0.111</v>
       </c>
       <c r="E2">
-        <v>0.112</v>
-      </c>
-      <c r="F2">
-        <v>0.103</v>
+        <v>0.365</v>
       </c>
       <c r="G2">
-        <v>0.08526455216601124</v>
+        <v>0.1876258369621202</v>
       </c>
       <c r="H2">
-        <v>0.08526455216601124</v>
+        <v>0.1876258369621202</v>
       </c>
       <c r="I2">
-        <v>0.1029742072998713</v>
+        <v>0.1768799456852554</v>
       </c>
       <c r="J2">
-        <v>0.07651673278016398</v>
+        <v>0.1442555472719597</v>
       </c>
       <c r="K2">
-        <v>4305.1</v>
+        <v>4051.2</v>
       </c>
       <c r="L2">
-        <v>0.0884085798482406</v>
+        <v>0.1185559769630566</v>
       </c>
       <c r="M2">
-        <v>1277.5</v>
+        <v>1839.3</v>
       </c>
       <c r="N2">
-        <v>0.02373988151429782</v>
+        <v>0.06023579498935648</v>
       </c>
       <c r="O2">
-        <v>0.2967410745394997</v>
+        <v>0.4540136255924171</v>
       </c>
       <c r="P2">
-        <v>850.5</v>
+        <v>363.1</v>
       </c>
       <c r="Q2">
-        <v>0.01580490741910786</v>
+        <v>0.0118912723104634</v>
       </c>
       <c r="R2">
-        <v>0.1975563866112285</v>
+        <v>0.0896277646129542</v>
       </c>
       <c r="S2">
-        <v>427.0000000000001</v>
+        <v>1476.2</v>
       </c>
       <c r="T2">
-        <v>0.3342465753424658</v>
+        <v>0.8025879410645355</v>
       </c>
       <c r="U2">
-        <v>6216.8</v>
+        <v>6420.2</v>
       </c>
       <c r="V2">
-        <v>0.1155272762411638</v>
+        <v>0.2102570820370067</v>
       </c>
       <c r="W2">
-        <v>0.1426423672643327</v>
+        <v>0.1999397890643122</v>
       </c>
       <c r="X2">
-        <v>0.07153970318863109</v>
+        <v>0.08178717655962991</v>
       </c>
       <c r="Y2">
-        <v>0.07110266407570157</v>
+        <v>0.1181526125046823</v>
       </c>
       <c r="Z2">
-        <v>1.543429326846343</v>
+        <v>1.322568409645082</v>
       </c>
       <c r="AA2">
-        <v>0.1530012084833439</v>
+        <v>0.1907878297379568</v>
       </c>
       <c r="AB2">
-        <v>0.06799391359697232</v>
+        <v>0.0713132962269777</v>
       </c>
       <c r="AC2">
-        <v>0.08512285167477601</v>
+        <v>0.1194745335109791</v>
       </c>
       <c r="AD2">
-        <v>12927.4</v>
+        <v>10710.9</v>
       </c>
       <c r="AE2">
-        <v>292.5974421455962</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>13219.9974421456</v>
+        <v>10710.9</v>
       </c>
       <c r="AG2">
-        <v>7003.197442145595</v>
+        <v>4290.7</v>
       </c>
       <c r="AH2">
-        <v>0.1972180310805015</v>
+        <v>0.259683992833227</v>
       </c>
       <c r="AI2">
-        <v>0.2498520747218614</v>
+        <v>0.2710076538680498</v>
       </c>
       <c r="AJ2">
-        <v>0.1151546270479016</v>
+        <v>0.1232049894187339</v>
       </c>
       <c r="AK2">
-        <v>0.1499790730336598</v>
+        <v>0.1296193920059936</v>
       </c>
       <c r="AL2">
-        <v>695.5599999999999</v>
+        <v>606.8</v>
       </c>
       <c r="AM2">
-        <v>695.5599999999999</v>
+        <v>606.8</v>
       </c>
       <c r="AN2">
-        <v>2.210340936292446</v>
+        <v>1.677168313420917</v>
       </c>
       <c r="AO2">
-        <v>7.194490770027029</v>
+        <v>9.960777851021755</v>
       </c>
       <c r="AP2">
-        <v>1.197414328582156</v>
+        <v>0.6718600754740616</v>
       </c>
       <c r="AQ2">
-        <v>7.194490770027029</v>
+        <v>9.960777851021755</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Definity Financial Corporation (TSX:DFY)</t>
+          <t>Fairfax Financial Holdings Limited (TSX:FFH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,521 +721,122 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.111</v>
+      </c>
+      <c r="E3">
+        <v>0.365</v>
+      </c>
       <c r="G3">
-        <v>0.0771151834227667</v>
+        <v>0.1876258369621202</v>
       </c>
       <c r="H3">
-        <v>0.0771151834227667</v>
+        <v>0.1876258369621202</v>
       </c>
       <c r="I3">
-        <v>0.1442408288616651</v>
+        <v>0.1768799456852554</v>
       </c>
       <c r="J3">
-        <v>0.1130918065841694</v>
+        <v>0.1442555472719597</v>
       </c>
       <c r="K3">
-        <v>332.9</v>
+        <v>4051.2</v>
       </c>
       <c r="L3">
-        <v>0.1123485538793831</v>
+        <v>0.1185559769630566</v>
       </c>
       <c r="M3">
-        <v>59.1</v>
+        <v>1839.3</v>
       </c>
       <c r="N3">
-        <v>0.01806455556914048</v>
+        <v>0.06023579498935648</v>
       </c>
       <c r="O3">
-        <v>0.1775307900270352</v>
+        <v>0.4540136255924171</v>
       </c>
       <c r="P3">
-        <v>45.7</v>
+        <v>363.1</v>
       </c>
       <c r="Q3">
-        <v>0.01396870033011371</v>
+        <v>0.0118912723104634</v>
       </c>
       <c r="R3">
-        <v>0.1372784620006008</v>
+        <v>0.0896277646129542</v>
       </c>
       <c r="S3">
-        <v>13.4</v>
+        <v>1476.2</v>
       </c>
       <c r="T3">
-        <v>0.2267343485617597</v>
+        <v>0.8025879410645355</v>
       </c>
       <c r="U3">
-        <v>299.5</v>
+        <v>6420.2</v>
       </c>
       <c r="V3">
-        <v>0.09154542120063577</v>
+        <v>0.2102570820370067</v>
       </c>
       <c r="W3">
-        <v>0.203957848302904</v>
+        <v>0.1999397890643122</v>
       </c>
       <c r="X3">
-        <v>0.06993001987997857</v>
+        <v>0.08178717655962991</v>
       </c>
       <c r="Y3">
-        <v>0.1340278284229255</v>
+        <v>0.1181526125046823</v>
       </c>
       <c r="Z3">
-        <v>1.966876866910056</v>
+        <v>1.322568409645082</v>
       </c>
       <c r="AA3">
-        <v>0.2224376582074691</v>
+        <v>0.1907878297379568</v>
       </c>
       <c r="AB3">
-        <v>0.06872587178532845</v>
+        <v>0.0713132962269777</v>
       </c>
       <c r="AC3">
-        <v>0.1537117864221407</v>
+        <v>0.1194745335109791</v>
       </c>
       <c r="AD3">
-        <v>110.6</v>
+        <v>10710.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>110.6</v>
+        <v>10710.9</v>
       </c>
       <c r="AG3">
-        <v>-188.9</v>
+        <v>4290.7</v>
       </c>
       <c r="AH3">
-        <v>0.03270060907101886</v>
+        <v>0.259683992833227</v>
       </c>
       <c r="AI3">
-        <v>0.05090206185567011</v>
+        <v>0.2710076538680498</v>
       </c>
       <c r="AJ3">
-        <v>-0.06127745158464983</v>
+        <v>0.1232049894187339</v>
       </c>
       <c r="AK3">
-        <v>-0.1008380932045054</v>
+        <v>0.1296193920059936</v>
       </c>
       <c r="AL3">
-        <v>2.66</v>
+        <v>606.8</v>
       </c>
       <c r="AM3">
-        <v>2.66</v>
+        <v>606.8</v>
       </c>
       <c r="AN3">
-        <v>0.2435050638485249</v>
+        <v>1.677168313420917</v>
       </c>
       <c r="AO3">
-        <v>160.6766917293233</v>
+        <v>9.960777851021755</v>
       </c>
       <c r="AP3">
-        <v>-0.4158960810215764</v>
+        <v>0.6718600754740616</v>
       </c>
       <c r="AQ3">
-        <v>160.6766917293233</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Trisura Group Ltd. (TSX:TSU)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.6409999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.112</v>
-      </c>
-      <c r="G4">
-        <v>0.0324630314232902</v>
-      </c>
-      <c r="H4">
-        <v>0.0324630314232902</v>
-      </c>
-      <c r="I4">
-        <v>0.05371996303142329</v>
-      </c>
-      <c r="J4">
-        <v>0.03029112754158965</v>
-      </c>
-      <c r="K4">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="L4">
-        <v>0.01005083179297597</v>
-      </c>
-      <c r="M4">
-        <v>1.2</v>
-      </c>
-      <c r="N4">
-        <v>0.0009828814808747644</v>
-      </c>
-      <c r="O4">
-        <v>0.1379310344827586</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>1.2</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4">
-        <v>392.9</v>
-      </c>
-      <c r="V4">
-        <v>0.3218117781964124</v>
-      </c>
-      <c r="W4">
-        <v>0.02269762588051135</v>
-      </c>
-      <c r="X4">
-        <v>0.07032365486842609</v>
-      </c>
-      <c r="Y4">
-        <v>-0.04762602898791475</v>
-      </c>
-      <c r="Z4">
-        <v>5.19256148770246</v>
-      </c>
-      <c r="AA4">
-        <v>0.1572885422915417</v>
-      </c>
-      <c r="AB4">
-        <v>0.06871193839593473</v>
-      </c>
-      <c r="AC4">
-        <v>0.08857660389560698</v>
-      </c>
-      <c r="AD4">
-        <v>62.8</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>62.8</v>
-      </c>
-      <c r="AG4">
-        <v>-330.1</v>
-      </c>
-      <c r="AH4">
-        <v>0.04892108748149879</v>
-      </c>
-      <c r="AI4">
-        <v>0.1242580134546893</v>
-      </c>
-      <c r="AJ4">
-        <v>-0.3705657835653344</v>
-      </c>
-      <c r="AK4">
-        <v>-2.93422222222222</v>
-      </c>
-      <c r="AL4">
-        <v>30.2</v>
-      </c>
-      <c r="AM4">
-        <v>30.2</v>
-      </c>
-      <c r="AN4">
-        <v>1.365217391304348</v>
-      </c>
-      <c r="AO4">
-        <v>1.539735099337748</v>
-      </c>
-      <c r="AP4">
-        <v>-7.176086956521738</v>
-      </c>
-      <c r="AQ4">
-        <v>1.539735099337748</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Fairfax Financial Holdings Limited (TSX:FFH)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.11</v>
-      </c>
-      <c r="E5">
-        <v>0.128</v>
-      </c>
-      <c r="G5">
-        <v>0.04442959801633994</v>
-      </c>
-      <c r="H5">
-        <v>0.04442959801633994</v>
-      </c>
-      <c r="I5">
-        <v>0.1064987469171503</v>
-      </c>
-      <c r="J5">
-        <v>0.08900203462225631</v>
-      </c>
-      <c r="K5">
-        <v>3144.4</v>
-      </c>
-      <c r="L5">
-        <v>0.1045144220861669</v>
-      </c>
-      <c r="M5">
-        <v>563</v>
-      </c>
-      <c r="N5">
-        <v>0.02583398338916166</v>
-      </c>
-      <c r="O5">
-        <v>0.179048467116143</v>
-      </c>
-      <c r="P5">
-        <v>245.2</v>
-      </c>
-      <c r="Q5">
-        <v>0.01125131923094572</v>
-      </c>
-      <c r="R5">
-        <v>0.0779799007759827</v>
-      </c>
-      <c r="S5">
-        <v>317.8</v>
-      </c>
-      <c r="T5">
-        <v>0.5644760213143872</v>
-      </c>
-      <c r="U5">
-        <v>4392.6</v>
-      </c>
-      <c r="V5">
-        <v>0.2015601339879778</v>
-      </c>
-      <c r="W5">
-        <v>0.2353011606414583</v>
-      </c>
-      <c r="X5">
-        <v>0.07801831769949268</v>
-      </c>
-      <c r="Y5">
-        <v>0.1572828429419657</v>
-      </c>
-      <c r="Z5">
-        <v>1.670904213665673</v>
-      </c>
-      <c r="AA5">
-        <v>0.1487138746751462</v>
-      </c>
-      <c r="AB5">
-        <v>0.06704477522120111</v>
-      </c>
-      <c r="AC5">
-        <v>0.08166909945394504</v>
-      </c>
-      <c r="AD5">
-        <v>8632</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>8632</v>
-      </c>
-      <c r="AG5">
-        <v>4239.4</v>
-      </c>
-      <c r="AH5">
-        <v>0.2837140509449466</v>
-      </c>
-      <c r="AI5">
-        <v>0.2521801370163163</v>
-      </c>
-      <c r="AJ5">
-        <v>0.1628509088674114</v>
-      </c>
-      <c r="AK5">
-        <v>0.1420858065013456</v>
-      </c>
-      <c r="AL5">
-        <v>505.2</v>
-      </c>
-      <c r="AM5">
-        <v>505.2</v>
-      </c>
-      <c r="AN5">
-        <v>2.377175589336858</v>
-      </c>
-      <c r="AO5">
-        <v>6.342240696753761</v>
-      </c>
-      <c r="AP5">
-        <v>1.167492839832562</v>
-      </c>
-      <c r="AQ5">
-        <v>6.342240696753761</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Intact Financial Corporation (TSX:IFC)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.139</v>
-      </c>
-      <c r="E6">
-        <v>0.0978</v>
-      </c>
-      <c r="F6">
-        <v>0.103</v>
-      </c>
-      <c r="G6">
-        <v>0.1731073675664705</v>
-      </c>
-      <c r="H6">
-        <v>0.1731073675664705</v>
-      </c>
-      <c r="I6">
-        <v>0.09041205003523989</v>
-      </c>
-      <c r="J6">
-        <v>0.07130244508336292</v>
-      </c>
-      <c r="K6">
-        <v>819.1</v>
-      </c>
-      <c r="L6">
-        <v>0.05541573641837494</v>
-      </c>
-      <c r="M6">
-        <v>654.2</v>
-      </c>
-      <c r="N6">
-        <v>0.02376584359299449</v>
-      </c>
-      <c r="O6">
-        <v>0.7986814796728117</v>
-      </c>
-      <c r="P6">
-        <v>559.6</v>
-      </c>
-      <c r="Q6">
-        <v>0.02032920525013714</v>
-      </c>
-      <c r="R6">
-        <v>0.6831888658283481</v>
-      </c>
-      <c r="S6">
-        <v>94.60000000000002</v>
-      </c>
-      <c r="T6">
-        <v>0.1446040966065424</v>
-      </c>
-      <c r="U6">
-        <v>1131.8</v>
-      </c>
-      <c r="V6">
-        <v>0.04111614457131024</v>
-      </c>
-      <c r="W6">
-        <v>0.08132688622576129</v>
-      </c>
-      <c r="X6">
-        <v>0.07275575150883611</v>
-      </c>
-      <c r="Y6">
-        <v>0.00857113471692518</v>
-      </c>
-      <c r="Z6">
-        <v>1.245104005862439</v>
-      </c>
-      <c r="AA6">
-        <v>0.08877896000108171</v>
-      </c>
-      <c r="AB6">
-        <v>0.06727588879800991</v>
-      </c>
-      <c r="AC6">
-        <v>0.02150307120307179</v>
-      </c>
-      <c r="AD6">
-        <v>4122</v>
-      </c>
-      <c r="AE6">
-        <v>292.5974421455962</v>
-      </c>
-      <c r="AF6">
-        <v>4414.597442145596</v>
-      </c>
-      <c r="AG6">
-        <v>3282.797442145596</v>
-      </c>
-      <c r="AH6">
-        <v>0.1382088441577163</v>
-      </c>
-      <c r="AI6">
-        <v>0.275850317911629</v>
-      </c>
-      <c r="AJ6">
-        <v>0.106550784807609</v>
-      </c>
-      <c r="AK6">
-        <v>0.2207397898550169</v>
-      </c>
-      <c r="AL6">
-        <v>157.5</v>
-      </c>
-      <c r="AM6">
-        <v>157.5</v>
-      </c>
-      <c r="AN6">
-        <v>2.40041928721174</v>
-      </c>
-      <c r="AO6">
-        <v>8.420317460317461</v>
-      </c>
-      <c r="AP6">
-        <v>1.911715258645234</v>
-      </c>
-      <c r="AQ6">
-        <v>8.420317460317461</v>
+        <v>9.960777851021755</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/canada/canada_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/canada/canada_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.111</v>
+        <v>0.222</v>
       </c>
       <c r="E2">
         <v>0.365</v>
       </c>
       <c r="G2">
-        <v>0.1876258369621202</v>
+        <v>0.1454596011630467</v>
       </c>
       <c r="H2">
-        <v>0.1876258369621202</v>
+        <v>0.1454596011630467</v>
       </c>
       <c r="I2">
-        <v>0.1768799456852554</v>
+        <v>0.145056674459463</v>
       </c>
       <c r="J2">
-        <v>0.1442555472719597</v>
+        <v>0.1123400364135653</v>
       </c>
       <c r="K2">
-        <v>4051.2</v>
+        <v>6127.3</v>
       </c>
       <c r="L2">
-        <v>0.1185559769630566</v>
+        <v>0.09848447101142956</v>
       </c>
       <c r="M2">
-        <v>1839.3</v>
+        <v>2685.2</v>
       </c>
       <c r="N2">
-        <v>0.06023579498935648</v>
+        <v>0.03895868365728778</v>
       </c>
       <c r="O2">
-        <v>0.4540136255924171</v>
+        <v>0.4382354381211954</v>
       </c>
       <c r="P2">
-        <v>363.1</v>
+        <v>1040.4</v>
       </c>
       <c r="Q2">
-        <v>0.0118912723104634</v>
+        <v>0.01509482142002168</v>
       </c>
       <c r="R2">
-        <v>0.0896277646129542</v>
+        <v>0.1697974638095083</v>
       </c>
       <c r="S2">
-        <v>1476.2</v>
+        <v>1644.8</v>
       </c>
       <c r="T2">
-        <v>0.8025879410645355</v>
+        <v>0.6125428273499182</v>
       </c>
       <c r="U2">
-        <v>6420.2</v>
+        <v>7616.5</v>
       </c>
       <c r="V2">
-        <v>0.2102570820370067</v>
+        <v>0.1105052934886535</v>
       </c>
       <c r="W2">
-        <v>0.1999397890643122</v>
+        <v>0.1928302650698877</v>
       </c>
       <c r="X2">
-        <v>0.08178717655962991</v>
+        <v>0.07653506958990064</v>
       </c>
       <c r="Y2">
-        <v>0.1181526125046823</v>
+        <v>0.116295195479987</v>
       </c>
       <c r="Z2">
-        <v>1.322568409645082</v>
+        <v>1.556703487148104</v>
       </c>
       <c r="AA2">
-        <v>0.1907878297379568</v>
+        <v>0.2156032715451306</v>
       </c>
       <c r="AB2">
-        <v>0.0713132962269777</v>
+        <v>0.07306391699538381</v>
       </c>
       <c r="AC2">
-        <v>0.1194745335109791</v>
+        <v>0.1431349699747121</v>
       </c>
       <c r="AD2">
-        <v>10710.9</v>
+        <v>15179.5</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>464.3422374874733</v>
       </c>
       <c r="AF2">
-        <v>10710.9</v>
+        <v>15643.84223748747</v>
       </c>
       <c r="AG2">
-        <v>4290.7</v>
+        <v>8027.342237487474</v>
       </c>
       <c r="AH2">
-        <v>0.259683992833227</v>
+        <v>0.1849850525692741</v>
       </c>
       <c r="AI2">
-        <v>0.2710076538680498</v>
+        <v>0.2582227489168913</v>
       </c>
       <c r="AJ2">
-        <v>0.1232049894187339</v>
+        <v>0.1043167111718495</v>
       </c>
       <c r="AK2">
-        <v>0.1296193920059936</v>
+        <v>0.15155581929892</v>
       </c>
       <c r="AL2">
-        <v>606.8</v>
+        <v>804.78</v>
       </c>
       <c r="AM2">
-        <v>606.8</v>
+        <v>804.78</v>
       </c>
       <c r="AN2">
-        <v>1.677168313420917</v>
+        <v>1.52972891262723</v>
       </c>
       <c r="AO2">
-        <v>9.960777851021755</v>
+        <v>11.15360719699794</v>
       </c>
       <c r="AP2">
-        <v>0.6718600754740616</v>
+        <v>0.808963240702154</v>
       </c>
       <c r="AQ2">
-        <v>9.960777851021755</v>
+        <v>11.15360719699794</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fairfax Financial Holdings Limited (TSX:FFH)</t>
+          <t>Trisura Group Ltd. (TSX:TSU)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,121 +722,517 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.111</v>
+        <v>0.887</v>
       </c>
       <c r="E3">
-        <v>0.365</v>
+        <v>1.126</v>
       </c>
       <c r="G3">
-        <v>0.1876258369621202</v>
+        <v>0.03202335124159229</v>
       </c>
       <c r="H3">
-        <v>0.1876258369621202</v>
+        <v>0.03202335124159229</v>
       </c>
       <c r="I3">
-        <v>0.1768799456852554</v>
+        <v>0.05465544227759211</v>
       </c>
       <c r="J3">
-        <v>0.1442555472719597</v>
+        <v>0.04099158170819408</v>
       </c>
       <c r="K3">
-        <v>4051.2</v>
+        <v>82.2</v>
       </c>
       <c r="L3">
-        <v>0.1185559769630566</v>
+        <v>0.03477304454503152</v>
       </c>
       <c r="M3">
-        <v>1839.3</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>0.06023579498935648</v>
+        <v>0.001551349674216568</v>
       </c>
       <c r="O3">
-        <v>0.4540136255924171</v>
+        <v>0.024330900243309</v>
       </c>
       <c r="P3">
-        <v>363.1</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0118912723104634</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.0896277646129542</v>
+        <v>-0</v>
       </c>
       <c r="S3">
-        <v>1476.2</v>
+        <v>2</v>
       </c>
       <c r="T3">
-        <v>0.8025879410645355</v>
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>6420.2</v>
+        <v>194.1</v>
       </c>
       <c r="V3">
-        <v>0.2102570820370067</v>
+        <v>0.1505584858827179</v>
       </c>
       <c r="W3">
-        <v>0.1999397890643122</v>
+        <v>0.1857207410754632</v>
       </c>
       <c r="X3">
-        <v>0.08178717655962991</v>
+        <v>0.07568994336646355</v>
       </c>
       <c r="Y3">
-        <v>0.1181526125046823</v>
+        <v>0.1100307977089996</v>
       </c>
       <c r="Z3">
-        <v>1.322568409645082</v>
+        <v>21.01244444444443</v>
       </c>
       <c r="AA3">
-        <v>0.1907878297379568</v>
+        <v>0.8613333333333328</v>
       </c>
       <c r="AB3">
-        <v>0.0713132962269777</v>
+        <v>0.0736519994068124</v>
       </c>
       <c r="AC3">
-        <v>0.1194745335109791</v>
+        <v>0.7876813339265204</v>
       </c>
       <c r="AD3">
-        <v>10710.9</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="AG3">
+        <v>-114.5</v>
+      </c>
+      <c r="AH3">
+        <v>0.0581531268264173</v>
+      </c>
+      <c r="AI3">
+        <v>0.1257901390644753</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.09747169490082574</v>
+      </c>
+      <c r="AK3">
+        <v>-0.2609984043765671</v>
+      </c>
+      <c r="AL3">
+        <v>19.4</v>
+      </c>
+      <c r="AM3">
+        <v>19.4</v>
+      </c>
+      <c r="AN3">
+        <v>0.6113671274961597</v>
+      </c>
+      <c r="AO3">
+        <v>6.65979381443299</v>
+      </c>
+      <c r="AP3">
+        <v>-0.8794162826420892</v>
+      </c>
+      <c r="AQ3">
+        <v>6.65979381443299</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Definity Financial Corporation (TSX:DFY)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="G4">
+        <v>0.1380163245115013</v>
+      </c>
+      <c r="H4">
+        <v>0.1380163245115013</v>
+      </c>
+      <c r="I4">
+        <v>0.1872037847281945</v>
+      </c>
+      <c r="J4">
+        <v>0.1402373410629039</v>
+      </c>
+      <c r="K4">
+        <v>399.5</v>
+      </c>
+      <c r="L4">
+        <v>0.1235159534998763</v>
+      </c>
+      <c r="M4">
+        <v>84.5</v>
+      </c>
+      <c r="N4">
+        <v>0.01815213421838414</v>
+      </c>
+      <c r="O4">
+        <v>0.2115143929912391</v>
+      </c>
+      <c r="P4">
+        <v>52.6</v>
+      </c>
+      <c r="Q4">
+        <v>0.01129943502824859</v>
+      </c>
+      <c r="R4">
+        <v>0.1316645807259074</v>
+      </c>
+      <c r="S4">
+        <v>31.9</v>
+      </c>
+      <c r="T4">
+        <v>0.3775147928994083</v>
+      </c>
+      <c r="U4">
+        <v>182</v>
+      </c>
+      <c r="V4">
+        <v>0.03909690447036583</v>
+      </c>
+      <c r="W4">
+        <v>0.2051874678993323</v>
+      </c>
+      <c r="X4">
+        <v>0.07547829157804378</v>
+      </c>
+      <c r="Y4">
+        <v>0.1297091763212885</v>
+      </c>
+      <c r="Z4">
+        <v>1.714370163681753</v>
+      </c>
+      <c r="AA4">
+        <v>0.2404187133523044</v>
+      </c>
+      <c r="AB4">
+        <v>0.07364043527579418</v>
+      </c>
+      <c r="AC4">
+        <v>0.1667782780765102</v>
+      </c>
+      <c r="AD4">
+        <v>112</v>
+      </c>
+      <c r="AE4">
+        <v>128.5403933756388</v>
+      </c>
+      <c r="AF4">
+        <v>240.5403933756388</v>
+      </c>
+      <c r="AG4">
+        <v>58.54039337563884</v>
+      </c>
+      <c r="AH4">
+        <v>0.04913359112346517</v>
+      </c>
+      <c r="AI4">
+        <v>0.09064885312321967</v>
+      </c>
+      <c r="AJ4">
+        <v>0.01241935924045228</v>
+      </c>
+      <c r="AK4">
+        <v>0.02368579268724156</v>
+      </c>
+      <c r="AL4">
+        <v>6.88</v>
+      </c>
+      <c r="AM4">
+        <v>6.88</v>
+      </c>
+      <c r="AN4">
+        <v>0.1551676364643945</v>
+      </c>
+      <c r="AO4">
+        <v>80.30523255813954</v>
+      </c>
+      <c r="AP4">
+        <v>0.08110334355173017</v>
+      </c>
+      <c r="AQ4">
+        <v>80.30523255813954</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Fairfax Financial Holdings Limited (TSX:FFH)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.111</v>
+      </c>
+      <c r="E5">
+        <v>0.365</v>
+      </c>
+      <c r="G5">
+        <v>0.1876258369621202</v>
+      </c>
+      <c r="H5">
+        <v>0.1876258369621202</v>
+      </c>
+      <c r="I5">
+        <v>0.1768799456852554</v>
+      </c>
+      <c r="J5">
+        <v>0.1442555472719597</v>
+      </c>
+      <c r="K5">
+        <v>4051.2</v>
+      </c>
+      <c r="L5">
+        <v>0.1185559769630566</v>
+      </c>
+      <c r="M5">
+        <v>1839.3</v>
+      </c>
+      <c r="N5">
+        <v>0.06023579498935648</v>
+      </c>
+      <c r="O5">
+        <v>0.4540136255924171</v>
+      </c>
+      <c r="P5">
+        <v>363.1</v>
+      </c>
+      <c r="Q5">
+        <v>0.0118912723104634</v>
+      </c>
+      <c r="R5">
+        <v>0.0896277646129542</v>
+      </c>
+      <c r="S5">
+        <v>1476.2</v>
+      </c>
+      <c r="T5">
+        <v>0.8025879410645355</v>
+      </c>
+      <c r="U5">
+        <v>6420.2</v>
+      </c>
+      <c r="V5">
+        <v>0.2102570820370067</v>
+      </c>
+      <c r="W5">
+        <v>0.1999397890643122</v>
+      </c>
+      <c r="X5">
+        <v>0.08176404000474105</v>
+      </c>
+      <c r="Y5">
+        <v>0.1181757490595712</v>
+      </c>
+      <c r="Z5">
+        <v>1.322568409645082</v>
+      </c>
+      <c r="AA5">
+        <v>0.1907878297379568</v>
+      </c>
+      <c r="AB5">
+        <v>0.07129616786504278</v>
+      </c>
+      <c r="AC5">
+        <v>0.119491661872914</v>
+      </c>
+      <c r="AD5">
         <v>10710.9</v>
       </c>
-      <c r="AG3">
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>10710.9</v>
+      </c>
+      <c r="AG5">
         <v>4290.7</v>
       </c>
-      <c r="AH3">
+      <c r="AH5">
         <v>0.259683992833227</v>
       </c>
-      <c r="AI3">
+      <c r="AI5">
         <v>0.2710076538680498</v>
       </c>
-      <c r="AJ3">
+      <c r="AJ5">
         <v>0.1232049894187339</v>
       </c>
-      <c r="AK3">
+      <c r="AK5">
         <v>0.1296193920059936</v>
       </c>
-      <c r="AL3">
+      <c r="AL5">
         <v>606.8</v>
       </c>
-      <c r="AM3">
+      <c r="AM5">
         <v>606.8</v>
       </c>
-      <c r="AN3">
+      <c r="AN5">
         <v>1.677168313420917</v>
       </c>
-      <c r="AO3">
+      <c r="AO5">
         <v>9.960777851021755</v>
       </c>
-      <c r="AP3">
+      <c r="AP5">
         <v>0.6718600754740616</v>
       </c>
-      <c r="AQ3">
+      <c r="AQ5">
         <v>9.960777851021755</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Intact Financial Corporation (TSX:IFC)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.222</v>
+      </c>
+      <c r="E6">
+        <v>0.232</v>
+      </c>
+      <c r="G6">
+        <v>0.09428683441442726</v>
+      </c>
+      <c r="H6">
+        <v>0.09428683441442726</v>
+      </c>
+      <c r="I6">
+        <v>0.1000578993147067</v>
+      </c>
+      <c r="J6">
+        <v>0.07836059047503896</v>
+      </c>
+      <c r="K6">
+        <v>1594.4</v>
+      </c>
+      <c r="L6">
+        <v>0.07103143488488131</v>
+      </c>
+      <c r="M6">
+        <v>759.4000000000001</v>
+      </c>
+      <c r="N6">
+        <v>0.02340576359993836</v>
+      </c>
+      <c r="O6">
+        <v>0.4762920220772704</v>
+      </c>
+      <c r="P6">
+        <v>624.7</v>
+      </c>
+      <c r="Q6">
+        <v>0.01925412236091848</v>
+      </c>
+      <c r="R6">
+        <v>0.3918088309081786</v>
+      </c>
+      <c r="S6">
+        <v>134.7</v>
+      </c>
+      <c r="T6">
+        <v>0.1773768764814327</v>
+      </c>
+      <c r="U6">
+        <v>820.2</v>
+      </c>
+      <c r="V6">
+        <v>0.02527970411465557</v>
+      </c>
+      <c r="W6">
+        <v>0.1532929526007115</v>
+      </c>
+      <c r="X6">
+        <v>0.07738019581333774</v>
+      </c>
+      <c r="Y6">
+        <v>0.07591275678737375</v>
+      </c>
+      <c r="Z6">
+        <v>1.850440350822408</v>
+      </c>
+      <c r="AA6">
+        <v>0.1450015985292821</v>
+      </c>
+      <c r="AB6">
+        <v>0.07248739871497345</v>
+      </c>
+      <c r="AC6">
+        <v>0.07251419981430865</v>
+      </c>
+      <c r="AD6">
+        <v>4277</v>
+      </c>
+      <c r="AE6">
+        <v>335.8018441118344</v>
+      </c>
+      <c r="AF6">
+        <v>4612.801844111835</v>
+      </c>
+      <c r="AG6">
+        <v>3792.601844111835</v>
+      </c>
+      <c r="AH6">
+        <v>0.1244758624247641</v>
+      </c>
+      <c r="AI6">
+        <v>0.2595266860686513</v>
+      </c>
+      <c r="AJ6">
+        <v>0.1046592945202881</v>
+      </c>
+      <c r="AK6">
+        <v>0.2237034648234679</v>
+      </c>
+      <c r="AL6">
+        <v>171.7</v>
+      </c>
+      <c r="AM6">
+        <v>171.7</v>
+      </c>
+      <c r="AN6">
+        <v>1.593101650091258</v>
+      </c>
+      <c r="AO6">
+        <v>13.10599883517764</v>
+      </c>
+      <c r="AP6">
+        <v>1.412672493802598</v>
+      </c>
+      <c r="AQ6">
+        <v>13.10599883517764</v>
       </c>
     </row>
   </sheetData>
